--- a/data/trending_integrated_20261026_15.xlsx
+++ b/data/trending_integrated_20261026_15.xlsx
@@ -581,10 +581,10 @@
         <v>185</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G2" t="n">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>59079182125</v>
+        <v>59084308935</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2075</v>
+        <v>2055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.74%</t>
+          <t>'+5.71%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>68542028358</v>
+        <v>69062804326</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5540</v>
+        <v>5560</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.91%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>43061758675</v>
+        <v>43273759190</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60200</v>
+        <v>60400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+1.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1.49</v>
       </c>
       <c r="E5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F5" t="n">
         <v>119</v>
       </c>
       <c r="G5" t="n">
-        <v>1061</v>
+        <v>1089</v>
       </c>
       <c r="H5" t="n">
         <v>40.39</v>
@@ -886,7 +886,7 @@
         <v>38.9</v>
       </c>
       <c r="O5" t="n">
-        <v>303239021700</v>
+        <v>308138633450</v>
       </c>
       <c r="P5" t="n">
         <v>67300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 호조 및 주식 소각 언급. 공매도 관련 분석 및 수급 기대감. 거래량 동반한 긍정적 추세 전망.</t>
+          <t>실적 개선 및 주식 소각 호재를 기반으로 한 숏커버링 기대감. 유동성 장세 속 프로그램 매수 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '수급']</t>
+          <t>['숏커버링', '주식소각', '유동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1282000</v>
+        <v>1280000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.39%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="G6" t="n">
-        <v>1909</v>
+        <v>1895</v>
       </c>
       <c r="H6" t="n">
         <v>48.69</v>
@@ -978,7 +978,7 @@
         <v>48.77</v>
       </c>
       <c r="O6" t="n">
-        <v>2608978944000</v>
+        <v>2669838609500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>이재명 정부 및 정치 관련 부정적 발언 다수. 투자 관련 실질적 내용 부족.</t>
+          <t>정치적 이슈에 대한 부정적인 언급이 주를 이루며, 투자 판단에 대한 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213500</v>
+        <v>213000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="G7" t="n">
-        <v>1919</v>
+        <v>1927</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1962313708500</v>
+        <v>1993664522250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16380</v>
+        <v>16330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.67%</t>
+          <t>'-2.97%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1156,19 +1156,19 @@
         <v>16820</v>
       </c>
       <c r="M8" t="n">
-        <v>16340</v>
+        <v>16320</v>
       </c>
       <c r="N8" t="n">
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>30125760265</v>
+        <v>31591445855</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>16340</v>
+        <v>16320</v>
       </c>
       <c r="R8" t="n">
         <v>414000</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57800</v>
+        <v>14240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02</v>
+        <v>0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="F9" t="n">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>641</v>
+        <v>212</v>
       </c>
       <c r="H9" t="n">
-        <v>22.23</v>
+        <v>10.03</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>59400</v>
+        <v>14700</v>
       </c>
       <c r="K9" t="n">
-        <v>58300</v>
+        <v>14370</v>
       </c>
       <c r="L9" t="n">
-        <v>59100</v>
+        <v>14770</v>
       </c>
       <c r="M9" t="n">
-        <v>57200</v>
+        <v>14100</v>
       </c>
       <c r="N9" t="n">
-        <v>22.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>72307294100</v>
+        <v>23390139940</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-72000</v>
+        <v>98000</v>
       </c>
       <c r="S9" t="n">
-        <v>-151000</v>
+        <v>-17000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
+          <t>주가 조작 및 공매도에 대한 강한 불만 표출. 정치적 이슈와 연관된 부정적 전망 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '정치적 요인']</t>
+          <t>['주가 조작', '공매도', '정치']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14280</v>
+        <v>57500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-3.20%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="G10" t="n">
-        <v>197</v>
+        <v>654</v>
       </c>
       <c r="H10" t="n">
-        <v>10.03</v>
+        <v>22.23</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14700</v>
+        <v>59400</v>
       </c>
       <c r="K10" t="n">
-        <v>14370</v>
+        <v>58300</v>
       </c>
       <c r="L10" t="n">
-        <v>14770</v>
+        <v>59100</v>
       </c>
       <c r="M10" t="n">
-        <v>14100</v>
+        <v>57200</v>
       </c>
       <c r="N10" t="n">
-        <v>9.890000000000001</v>
+        <v>22.25</v>
       </c>
       <c r="O10" t="n">
-        <v>22964265590</v>
+        <v>74286801250</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>98000</v>
+        <v>-72000</v>
       </c>
       <c r="S10" t="n">
-        <v>-17000</v>
+        <v>-151000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도에 대한 강한 불만 표출. 정치적 이슈와 연관된 부정적 전망 제기.</t>
+          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '정치']</t>
+          <t>['원전', '정치적 요인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26750</v>
+        <v>26550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.98%</t>
+          <t>'-6.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>55691656175</v>
+        <v>56833116275</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3075</v>
+        <v>3045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.29%</t>
+          <t>'-20.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G12" t="n">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26072812870</v>
+        <v>26481825700</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_15.xlsx
+++ b/data/trending_integrated_20261026_15.xlsx
@@ -578,10 +578,10 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
         <v>670</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>59084308935</v>
+        <v>59125338105</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.71%</t>
+          <t>'+6.22%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
         <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>69062804326</v>
+        <v>69499033488</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5560</v>
+        <v>5610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.28%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
         <v>190</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>43273759190</v>
+        <v>43429087110</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급과 함께 주가 상승에 대한 기대감 표출. 일부 부정적 언급 존재.</t>
+          <t>정치 테마주 관련 논쟁과 함께 진양화학과의 비교 언급. 향후 주가 상승에 대한 기대감 표현.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마', '우상향', '물려있습니다']</t>
+          <t>['정치 테마주', '진양화학', '주가 상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60400</v>
+        <v>60200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.00%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1.49</v>
       </c>
       <c r="E5" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F5" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G5" t="n">
-        <v>1089</v>
+        <v>1079</v>
       </c>
       <c r="H5" t="n">
         <v>40.39</v>
@@ -886,7 +886,7 @@
         <v>38.9</v>
       </c>
       <c r="O5" t="n">
-        <v>308138633450</v>
+        <v>315261989350</v>
       </c>
       <c r="P5" t="n">
         <v>67300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 개선 및 주식 소각 호재를 기반으로 한 숏커버링 기대감. 유동성 장세 속 프로그램 매수 가능성 언급.</t>
+          <t>본격적인 호재 시작 전으로 판단하며, 기술적 분석 기반 매매 기회 강조. 실적 호조와 주식 소각에 대한 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['숏커버링', '주식소각', '유동성']</t>
+          <t>['기술적 분석', '실적 호조', '주식 소각']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1280000</v>
+        <v>1279000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G6" t="n">
-        <v>1895</v>
+        <v>1925</v>
       </c>
       <c r="H6" t="n">
         <v>48.69</v>
@@ -978,7 +978,7 @@
         <v>48.77</v>
       </c>
       <c r="O6" t="n">
-        <v>2669838609500</v>
+        <v>2725009926000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 부정적인 언급이 주를 이루며, 투자 판단에 대한 근거 제시 부족.</t>
+          <t>현 정권에 대한 강한 비판과 함께 이재명 대통령 관련 부정적 언급. 주가 하락에 대한 우려와 탈출 희망 표현.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정권 비판', '주가 하락', '이재명']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1044,7 +1044,7 @@
         <v>471</v>
       </c>
       <c r="G7" t="n">
-        <v>1927</v>
+        <v>2002</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1993664522250</v>
+        <v>2039385246000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명 정부에 대한 정치적 불만 표출. 주가 관련 내용은 거의 없음.</t>
+          <t>이재명 정부의 정책 실패에 대한 비판적 의견과 외인 매도 우려 제기. 증시 하락에 대한 정부 책임론 부각.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정부 정책', '외인 매도', '증시 하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16330</v>
+        <v>16300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.97%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1156,19 +1156,19 @@
         <v>16820</v>
       </c>
       <c r="M8" t="n">
-        <v>16320</v>
+        <v>16290</v>
       </c>
       <c r="N8" t="n">
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>31591445855</v>
+        <v>32898694040</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>16320</v>
+        <v>16290</v>
       </c>
       <c r="R8" t="n">
         <v>414000</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14240</v>
+        <v>57500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-3.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>156</v>
       </c>
       <c r="G9" t="n">
-        <v>212</v>
+        <v>686</v>
       </c>
       <c r="H9" t="n">
-        <v>10.03</v>
+        <v>22.23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14700</v>
+        <v>59400</v>
       </c>
       <c r="K9" t="n">
-        <v>14370</v>
+        <v>58300</v>
       </c>
       <c r="L9" t="n">
-        <v>14770</v>
+        <v>59100</v>
       </c>
       <c r="M9" t="n">
-        <v>14100</v>
+        <v>57200</v>
       </c>
       <c r="N9" t="n">
-        <v>9.890000000000001</v>
+        <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>23390139940</v>
+        <v>77886913200</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>98000</v>
+        <v>-72000</v>
       </c>
       <c r="S9" t="n">
-        <v>-17000</v>
+        <v>-151000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도에 대한 강한 불만 표출. 정치적 이슈와 연관된 부정적 전망 제기.</t>
+          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '정치']</t>
+          <t>['원전', '정치적 요인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57500</v>
+        <v>14220</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.20%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.02</v>
+        <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>654</v>
+        <v>214</v>
       </c>
       <c r="H10" t="n">
-        <v>22.23</v>
+        <v>10.03</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>59400</v>
+        <v>14700</v>
       </c>
       <c r="K10" t="n">
-        <v>58300</v>
+        <v>14370</v>
       </c>
       <c r="L10" t="n">
-        <v>59100</v>
+        <v>14770</v>
       </c>
       <c r="M10" t="n">
-        <v>57200</v>
+        <v>14100</v>
       </c>
       <c r="N10" t="n">
-        <v>22.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>74286801250</v>
+        <v>24067861505</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-72000</v>
+        <v>98000</v>
       </c>
       <c r="S10" t="n">
-        <v>-151000</v>
+        <v>-17000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
+          <t>주가 조작 및 공매도에 대한 강한 불만 표출. 정치적 이슈와 연관된 부정적 전망 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '정치적 요인']</t>
+          <t>['주가 조작', '공매도', '정치']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F11" t="n">
         <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1432,13 +1432,13 @@
         <v>28200</v>
       </c>
       <c r="M11" t="n">
-        <v>26550</v>
+        <v>26500</v>
       </c>
       <c r="N11" t="n">
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>56833116275</v>
+        <v>58221848825</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3045</v>
+        <v>3065</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-20.08%</t>
+          <t>'-19.55%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="F12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G12" t="n">
         <v>489</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26481825700</v>
+        <v>26765159255</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_15.xlsx
+++ b/data/trending_integrated_20261026_15.xlsx
@@ -584,7 +584,7 @@
         <v>125</v>
       </c>
       <c r="G2" t="n">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>59125338105</v>
+        <v>59266670595</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 투자 및 기술 개발에 대한 긍정적 전망. 공매도 청산 기대감 형성.</t>
+          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와 협력 등 구체적인 호재 기반 긍정적 전망. 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '공매도', '임상']</t>
+          <t>['AI 신약', '빅파마', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2065</v>
+        <v>2035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.22%</t>
+          <t>'+4.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>69499033488</v>
+        <v>69762201723</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5610</v>
+        <v>5560</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.19%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>43429087110</v>
+        <v>43572462830</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 논쟁과 함께 진양화학과의 비교 언급. 향후 주가 상승에 대한 기대감 표현.</t>
+          <t>정치 테마주 관련 언급과 함께 주가 상승 기대감 표출. 일부 부정적 의견 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '진양화학', '주가 상승']</t>
+          <t>['정치 테마주', '주가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60200</v>
+        <v>59800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>221</v>
       </c>
       <c r="F5" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G5" t="n">
-        <v>1079</v>
+        <v>1097</v>
       </c>
       <c r="H5" t="n">
         <v>40.39</v>
@@ -886,7 +886,7 @@
         <v>38.9</v>
       </c>
       <c r="O5" t="n">
-        <v>315261989350</v>
+        <v>321182607950</v>
       </c>
       <c r="P5" t="n">
         <v>67300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>본격적인 호재 시작 전으로 판단하며, 기술적 분석 기반 매매 기회 강조. 실적 호조와 주식 소각에 대한 긍정적 전망 제시.</t>
+          <t>실적 호조, 주식 소각 등 구체적인 호재 언급과 함께 매수 추천. 기술적 분석 및 수급 동향 긍정적 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['기술적 분석', '실적 호조', '주식 소각']</t>
+          <t>['실적', '주식 소각', '기술적 분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1279000</v>
+        <v>1275000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'-0.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G6" t="n">
-        <v>1925</v>
+        <v>2100</v>
       </c>
       <c r="H6" t="n">
         <v>48.69</v>
@@ -978,7 +978,7 @@
         <v>48.77</v>
       </c>
       <c r="O6" t="n">
-        <v>2725009926000</v>
+        <v>3015138726000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>현 정권에 대한 강한 비판과 함께 이재명 대통령 관련 부정적 언급. 주가 하락에 대한 우려와 탈출 희망 표현.</t>
+          <t>정치적 이슈 및 증시 상황에 대한 강한 불만 표출. 주가에 대한 부정적 전망 및 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정권 비판', '주가 하락', '이재명']</t>
+          <t>['증시', '주가조작', '무능정권']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G7" t="n">
-        <v>2002</v>
+        <v>2053</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>2039385246000</v>
+        <v>2326192089000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명 정부의 정책 실패에 대한 비판적 의견과 외인 매도 우려 제기. 증시 하락에 대한 정부 책임론 부각.</t>
+          <t>정치적 이슈와 관련된 부정적 언급 다수, 주가 관련 구체적인 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정부 정책', '외인 매도', '증시 하락']</t>
+          <t>['정권', '정치']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16300</v>
+        <v>57600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.15%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>99</v>
+        <v>210</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="G8" t="n">
-        <v>261</v>
+        <v>711</v>
       </c>
       <c r="H8" t="n">
-        <v>27.94</v>
+        <v>22.23</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16830</v>
+        <v>59400</v>
       </c>
       <c r="K8" t="n">
-        <v>16520</v>
+        <v>58300</v>
       </c>
       <c r="L8" t="n">
-        <v>16820</v>
+        <v>59100</v>
       </c>
       <c r="M8" t="n">
-        <v>16290</v>
+        <v>57200</v>
       </c>
       <c r="N8" t="n">
-        <v>27.89</v>
+        <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>32898694040</v>
+        <v>86363329200</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>16290</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>414000</v>
+        <v>-72000</v>
       </c>
       <c r="S8" t="n">
-        <v>-110000</v>
+        <v>-151000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국내 조선업의 경쟁력 약화와 관련된 부정적 뉴스 언급. 주가 하락 및 상장 폐지 우려.</t>
+          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['조선', '수주', '실적']</t>
+          <t>['원전', '정치적 요인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57500</v>
+        <v>16300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.20%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>202</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>686</v>
+        <v>266</v>
       </c>
       <c r="H9" t="n">
-        <v>22.23</v>
+        <v>27.94</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>59400</v>
+        <v>16830</v>
       </c>
       <c r="K9" t="n">
-        <v>58300</v>
+        <v>16520</v>
       </c>
       <c r="L9" t="n">
-        <v>59100</v>
+        <v>16820</v>
       </c>
       <c r="M9" t="n">
-        <v>57200</v>
+        <v>16290</v>
       </c>
       <c r="N9" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="O9" t="n">
-        <v>77886913200</v>
+        <v>36505655840</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>16290</v>
       </c>
       <c r="R9" t="n">
-        <v>-72000</v>
+        <v>414000</v>
       </c>
       <c r="S9" t="n">
-        <v>-151000</v>
+        <v>-110000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
+          <t>국내 조선업의 경쟁력 약화와 관련된 부정적 뉴스 언급. 주가 하락 및 상장 폐지 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '정치적 요인']</t>
+          <t>['조선', '수주', '실적']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>24067861505</v>
+        <v>25013463065</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26550</v>
+        <v>26500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.68%</t>
+          <t>'-6.85%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>58221848825</v>
+        <v>60713855825</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3065</v>
+        <v>3075</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.55%</t>
+          <t>'-19.29%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G12" t="n">
         <v>489</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26765159255</v>
+        <v>26908288205</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>지정학적 리스크 테마주 언급. 급락 및 부정적 전망 다수.</t>
+          <t>전쟁 테마 관련 언급과 함께 주가 급락. 투기적 거래 및 허위 정보 유포에 대한 경고.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['지정학적 리스크']</t>
+          <t>['전쟁 테마', '주가 급락', '투기']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_15.xlsx
+++ b/data/trending_integrated_20261026_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G2" t="n">
-        <v>688</v>
+        <v>701</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와 협력 등 구체적인 호재 기반 긍정적 전망. 공매도 세력에 대한 언급.</t>
+          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마 협력 등 구체적인 호재와 함께 차세대 면역항암제 관련 긍정적 전망이 제시되었습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '빅파마', '공매도']</t>
+          <t>['AI', '신약', '면역항암제']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3" t="n">
         <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>69762201723</v>
+        <v>69774002688</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -762,13 +762,13 @@
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F4" t="n">
         <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>43572462830</v>
+        <v>43572590710</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급과 함께 주가 상승 기대감 표출. 일부 부정적 의견 존재.</t>
+          <t>정치 테마주 관련 언급과 함께 긍정적 전망 일부 포함되었으나, 구체적인 근거 없이 감정적인 표현이 주를 이룹니다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '주가']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>1.49</v>
       </c>
       <c r="E5" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F5" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
-        <v>1097</v>
+        <v>1120</v>
       </c>
       <c r="H5" t="n">
         <v>40.39</v>
@@ -886,7 +886,7 @@
         <v>38.9</v>
       </c>
       <c r="O5" t="n">
-        <v>321182607950</v>
+        <v>321326546550</v>
       </c>
       <c r="P5" t="n">
         <v>67300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 호조, 주식 소각 등 구체적인 호재 언급과 함께 매수 추천. 기술적 분석 및 수급 동향 긍정적 전망.</t>
+          <t>실적 호조 및 주식 소각 예정 언급, 기술적 분석 기반의 매수 기회 강조 등 긍정적 전망의 근거가 일부 제시되었습니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', '주식 소각', '기술적 분석']</t>
+          <t>['실적', '전망']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="G6" t="n">
-        <v>2100</v>
+        <v>2329</v>
       </c>
       <c r="H6" t="n">
         <v>48.69</v>
@@ -978,7 +978,7 @@
         <v>48.77</v>
       </c>
       <c r="O6" t="n">
-        <v>3015138726000</v>
+        <v>3021625926000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 증시 상황에 대한 강한 불만 표출. 주가에 대한 부정적 전망 및 투자 심리 위축.</t>
+          <t>정치적 비판과 함께 주가 조작 의혹 및 거래 행태에 대한 불만이 제기되었으나, 객관적인 사실이나 분석은 부족합니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['증시', '주가조작', '무능정권']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="G7" t="n">
-        <v>2053</v>
+        <v>2150</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>2326192089000</v>
+        <v>2326352052000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급 다수, 주가 관련 구체적인 근거 제시 부족.</t>
+          <t>정치 관련 부정적 언급이 다수 포함되었으며, 외인 매도 언급이 있으나 구체적인 근거나 분석은 부재합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정권', '정치']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F8" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G8" t="n">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>86363329200</v>
+        <v>86371393200</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
+          <t>주가 하락에 대한 정치적 책임론 제기와 함께 부정적인 전망이 주를 이루며, 일부 신용 거래 관련 언급이 있으나 분석은 미흡합니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '정치적 요인']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="H9" t="n">
         <v>27.94</v>
@@ -1254,7 +1254,7 @@
         <v>27.89</v>
       </c>
       <c r="O9" t="n">
-        <v>36505655840</v>
+        <v>36507334740</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1320,7 +1320,7 @@
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>25013463065</v>
+        <v>25021923965</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>60713855825</v>
+        <v>60790573325</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F12" t="n">
         <v>148</v>
       </c>
       <c r="G12" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26908288205</v>
+        <v>26917679255</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_15.xlsx
+++ b/data/trending_integrated_20261026_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>701</v>
+        <v>719</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -676,7 +676,7 @@
         <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>69774002688</v>
+        <v>69781129258</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -762,13 +762,13 @@
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>43572590710</v>
+        <v>43573035510</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급과 함께 긍정적 전망 일부 포함되었으나, 구체적인 근거 없이 감정적인 표현이 주를 이룹니다.</t>
+          <t>정치 테마주 관련 언급과 함께 일부 긍정적 전망이 제시되었으나, 구체적인 실적이나 공시 기반 분석은 미흡함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치 테마주', '우상향 전망', '재료 소멸']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>1.49</v>
       </c>
       <c r="E5" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F5" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G5" t="n">
-        <v>1120</v>
+        <v>1136</v>
       </c>
       <c r="H5" t="n">
         <v>40.39</v>
@@ -886,7 +886,7 @@
         <v>38.9</v>
       </c>
       <c r="O5" t="n">
-        <v>321326546550</v>
+        <v>321377914750</v>
       </c>
       <c r="P5" t="n">
         <v>67300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 호조 및 주식 소각 예정 언급, 기술적 분석 기반의 매수 기회 강조 등 긍정적 전망의 근거가 일부 제시되었습니다.</t>
+          <t>실적 호조 및 주식 소각 등의 긍정적 요인이 언급되었으며, 기술적 분석과 수급 동향을 바탕으로 상승 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', '전망']</t>
+          <t>['실적 호조', '주식 소각', '기술적 분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G6" t="n">
-        <v>2329</v>
+        <v>2349</v>
       </c>
       <c r="H6" t="n">
         <v>48.69</v>
@@ -978,7 +978,7 @@
         <v>48.77</v>
       </c>
       <c r="O6" t="n">
-        <v>3021625926000</v>
+        <v>3021738126000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 비판과 함께 주가 조작 의혹 및 거래 행태에 대한 불만이 제기되었으나, 객관적인 사실이나 분석은 부족합니다.</t>
+          <t>주가 조작 및 시장 불신에 대한 강한 불만과 부정적 인식이 다수 확인되었으나, 객관적인 팩트 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['주가 조작', '시장 불신', '부정적 전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G7" t="n">
-        <v>2150</v>
+        <v>2143</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>2326352052000</v>
+        <v>2326411266000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치 관련 부정적 언급이 다수 포함되었으며, 외인 매도 언급이 있으나 구체적인 근거나 분석은 부재합니다.</t>
+          <t>정치권 이슈와 연관된 부정적 언급이 다수 확인되었으며, 주가 하락에 대한 언급이 있으나 구체적인 팩트 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치', '주가 하락', '부정적 전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F8" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G8" t="n">
-        <v>723</v>
+        <v>772</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>86371393200</v>
+        <v>86373524400</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 정치적 책임론 제기와 함께 부정적인 전망이 주를 이루며, 일부 신용 거래 관련 언급이 있으나 분석은 미흡합니다.</t>
+          <t>회사 및 한국 증시에 대한 강한 불신과 부정적 인식이 지배적이며, 주가 급락에 대한 언급이 많으나 구체적인 팩트 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['증시 불신', '주가 급락', '부정적 전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H9" t="n">
         <v>27.94</v>
@@ -1254,7 +1254,7 @@
         <v>27.89</v>
       </c>
       <c r="O9" t="n">
-        <v>36507334740</v>
+        <v>36508769140</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1314,13 +1314,13 @@
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>25021923965</v>
+        <v>25028593145</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" t="n">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>60790573325</v>
+        <v>60811905825</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1504,7 +1504,7 @@
         <v>148</v>
       </c>
       <c r="G12" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26917679255</v>
+        <v>26920785005</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>전쟁 테마 관련 언급과 함께 주가 급락. 투기적 거래 및 허위 정보 유포에 대한 경고.</t>
+          <t>전쟁 관련 테마주 언급과 함께 급락에 대한 경고가 나타났으며, 투자 주의 및 소문 기반 매수 자제 의견이 제시됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['전쟁 테마', '주가 급락', '투기']</t>
+          <t>['테마주', '급락 경고', '투자 주의']</t>
         </is>
       </c>
       <c r="X12" t="n">
